--- a/utilitaires/document-informatif/FICHE DE PAIE .xlsx
+++ b/utilitaires/document-informatif/FICHE DE PAIE .xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TOVO\Cours Gestion\RH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\itu\s5\gestion entreprise\projet\module-rh\utilitaires\document-informatif\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB572790-3409-4FB8-A62A-896D986B1EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FICHE" sheetId="1" r:id="rId1"/>
@@ -33,7 +34,21 @@
     <definedName name="OSTIE">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">FICHE!$B$2:$K$64</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -238,22 +253,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="14">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="00&quot; jour(s)&quot;"/>
-    <numFmt numFmtId="167" formatCode="00&quot; an(s)&quot;"/>
-    <numFmt numFmtId="168" formatCode="00&quot; mois&quot;"/>
-    <numFmt numFmtId="169" formatCode="&quot;ARRETE AU &quot;dd/mm/yy"/>
-    <numFmt numFmtId="170" formatCode="00.0&quot; jour(s)&quot;"/>
-    <numFmt numFmtId="171" formatCode="000"/>
-    <numFmt numFmtId="172" formatCode="#,##0&quot; FMG&quot;"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00&quot; Jour(s)&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00&quot; heure(s)&quot;"/>
-    <numFmt numFmtId="175" formatCode="[h]:mm"/>
-    <numFmt numFmtId="176" formatCode="&quot;Déduction pour charges de famille : &quot;#,##0"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="00&quot; jour(s)&quot;"/>
+    <numFmt numFmtId="166" formatCode="00&quot; an(s)&quot;"/>
+    <numFmt numFmtId="167" formatCode="00&quot; mois&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;ARRETE AU &quot;dd/mm/yy"/>
+    <numFmt numFmtId="169" formatCode="00.0&quot; jour(s)&quot;"/>
+    <numFmt numFmtId="170" formatCode="000"/>
+    <numFmt numFmtId="171" formatCode="#,##0&quot; FMG&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00&quot; Jour(s)&quot;"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00&quot; heure(s)&quot;"/>
+    <numFmt numFmtId="174" formatCode="[h]:mm"/>
+    <numFmt numFmtId="175" formatCode="&quot;Déduction pour charges de famille : &quot;#,##0"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -734,9 +749,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -756,7 +771,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -766,7 +781,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -782,7 +797,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -795,28 +810,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,11 +859,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
@@ -882,7 +897,7 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,7 +916,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -944,7 +959,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="12" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -962,32 +977,32 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="173" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="174" fontId="12" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="175" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1011,7 +1026,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1139,7 +1154,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1220,14 +1235,14 @@
     </xf>
   </cellXfs>
   <cellStyles count="9">
-    <cellStyle name="Euro" xfId="4"/>
-    <cellStyle name="Milliers 3" xfId="5"/>
-    <cellStyle name="Milliers 3 2" xfId="3"/>
-    <cellStyle name="Milliers 7" xfId="6"/>
+    <cellStyle name="Euro" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Milliers 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Milliers 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Milliers 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="7"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 11" xfId="8"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 2 11" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1260,7 +1275,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1501,6 +1522,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1536,6 +1574,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1711,7 +1766,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4175,7 +4230,7 @@
     <row r="100" ht="13.2" x14ac:dyDescent="0.25"/>
     <row r="101" ht="13.2" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="H22:J37"/>
+  <autoFilter ref="H22:J37" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.78740157480314965" bottom="0.78740157480314965" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="69" fitToHeight="5000" orientation="portrait" horizontalDpi="400" verticalDpi="400" r:id="rId1"/>
